--- a/04_DESIGN_TABLES/DesignTable_2611.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2611.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,55 +461,60 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>THDMAJ_B@DRIVE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>THDMAJ_A2@DRIVE</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>THDMAJ_A3@DRIVE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@TubeOD</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>$PRP@Threads</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -542,46 +547,46 @@
       <c r="H3" t="n">
         <v>0.43</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.4375</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.54</v>
       </c>
       <c r="K3" t="n">
         <v>0.54</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2611-04-04-04</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>7/16-20 (B UN/UNF-2A) x 1/4-18 (A (2) NPTF) x 1/4-18 (A (3) NPTF)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Air-Way s179 only (double-pass 5 rows)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -614,46 +619,46 @@
       <c r="H4" t="n">
         <v>0.57</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.5625</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.675</v>
       </c>
       <c r="K4" t="n">
         <v>0.675</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>3/8</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2611-06-06-06</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>9/16-18 (B UN/UNF-2A) x 3/8-18 (A (2) NPTF) x 3/8-18 (A (3) NPTF)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Air-Way s179 only (double-pass 5 rows)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2611-06-06-06-FG</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -686,46 +691,46 @@
       <c r="H5" t="n">
         <v>0.57</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.75</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.675</v>
       </c>
       <c r="K5" t="n">
         <v>0.675</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2611-08-06-06</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>3/4-16 (B UN/UNF-2A) x 3/8-18 (A (2) NPTF) x 3/8-18 (A (3) NPTF)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Air-Way s179 only (double-pass 5 rows)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -758,46 +763,46 @@
       <c r="H6" t="n">
         <v>0.91</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.0625</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.05</v>
       </c>
       <c r="K6" t="n">
         <v>1.05</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2611-12-12-12</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1 1/16-12 (B UN/UNF-2A) x 3/4-14 (A (2) NPTF) x 3/4-14 (A (3) NPTF)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Air-Way s179 only (double-pass 5 rows)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2611-12-12-12-FG</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -830,46 +835,46 @@
       <c r="H7" t="n">
         <v>1.14</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1.3125</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.315</v>
       </c>
       <c r="K7" t="n">
         <v>1.315</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2611-16-16-16</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>1 5/16-12 (B UN/UNF-2A) x 1-11 1/2 (A (2) NPTF) x 1-11 1/2 (A (3) NPTF)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Air-Way s179 only (double-pass 5 rows)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -881,32 +886,62 @@
           <t>2611-06-06-06-FG</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2611-06-06-06-FG</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M1@DRIVE: OMi Items row 885 M 1 Size = 1.310; N5@DRIVE: OMi Items row 885 M 2 Size = 1.220; N1@DRIVE: OMi Items row 885 L 1 Size = 1.020; Y1@HEX: OMi Items row 885 Hex Flat = 0.875; D@BORE: OMi Items row 885 Side 1 ID = 0.297; D1@BORE: OMi Items row 885 Side 2 ID = 0.406; THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (end library); THDMAJ_A2@DRIVE: 3/8-18 -&gt; 0.675 (end library); THDMAJ_A3@DRIVE: 3/8-18 -&gt; 0.675 (end library); TAPDRILL@BORE: end-library tap drill of the -06 pipe port = 0.57 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 885, ports from the end library (not from its own Brennan file) - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2611-06-06-06-FG</t>
         </is>
@@ -918,32 +953,62 @@
           <t>2611-08-08-08-FG</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2611-08-08-08-FG</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 2 ID = JIC leg / male pipe leg / female pipe branch leg / body hex / JIC bore / male pipe bore (Brennan TFA catalog p52 drawing M / L / L1 / Y / B1 / A2; Brennan 2611-06-06-06-FG STEP: 1.310 / 1.220 / 1.020, A/F 0.875, bores 0.297 / 0.406 = OMi row 885)); OMi = Brennan data (Brennan catalog TFA p52 (MJ-MP-FP TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2611-08-08-08-FG</t>
         </is>
@@ -955,32 +1020,41 @@
           <t>2611-12-12-12-FG</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2611-12-12-12-FG</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 2 ID = JIC leg / male pipe leg / female pipe branch leg / body hex / JIC bore / male pipe bore (Brennan TFA catalog p52 drawing M / L / L1 / Y / B1 / A2; Brennan 2611-06-06-06-FG STEP: 1.310 / 1.220 / 1.020, A/F 0.875, bores 0.297 / 0.406 = OMi row 885)); OMi = Brennan data (Brennan catalog TFA p52 (MJ-MP-FP TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING - OMi gives no body dimensions for this part (M1@DRIVE, N5@DRIVE, N1@DRIVE, Y1@HEX, D@BORE, D1@BORE); the Brennan catalog TFA p52 (MJ-MP-FP TEE) prints them, but a Brennan-only value is not filled until Q-BRENNAN-ONLY is answered (proposals/); also no female-port tap drill / thread length source | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2611-12-12-12-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_2611.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2611.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1020,6 +1025,27 @@
           <t>2611-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.91</v>
+      </c>
       <c r="J10" t="n">
         <v>1.0625</v>
       </c>
@@ -1036,17 +1062,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 2 ID = JIC leg / male pipe leg / female pipe branch leg / body hex / JIC bore / male pipe bore (Brennan TFA catalog p52 drawing M / L / L1 / Y / B1 / A2; Brennan 2611-06-06-06-FG STEP: 1.310 / 1.220 / 1.020, A/F 0.875, bores 0.297 / 0.406 = OMi row 885)); OMi = Brennan data (Brennan catalog TFA p52 (MJ-MP-FP TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] 2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 2 ID = JIC leg / male pipe leg / female pipe branch leg / body hex / JIC bore / male pipe bore (Brennan TFA catalog p52 drawing M / L / L1 / Y / B1 / A2; Brennan 2611-06-06-06-FG STEP: 1.310 / 1.220 / 1.020, A/F 0.875, bores 0.297 / 0.406 = OMi row 885)); OMi = Brennan data (Brennan catalog TFA p52 (MJ-MP-FP TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M1@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "M LGTH" = "1.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the B1 JIC tip (column mapping: REPORT.md, table 2611); N5@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "L LGTH" = "1.590" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the A2 male NPTF tip (column mapping: REPORT.md, table 2611); N1@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "L1 LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the A3 female NPTF port face (column mapping: REPORT.md, table 2611); Y1@HEX: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2611); D@BORE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - JIC drill (column mapping: REPORT.md, table 2611); D1@BORE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - male NPTF drill (column mapping: REPORT.md, table 2611); TAPDRILL@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-ENDLIB yes 2026-10-08: tap drills from the end library; = A1 YES 2026-10-18]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-02 (JIC-TEES): stays MISSING - OMi gives no body dimensions for this part (M1@DRIVE, N5@DRIVE, N1@DRIVE, Y1@HEX, D@BORE, D1@BORE); the Brennan catalog TFA p52 (MJ-MP-FP TEE) prints them, but a Brennan-only value is not filled until Q-BRENNAN-ONLY is answered (proposals/); also no female-port tap drill / thread length source | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 (JIC-TEES): stays MISSING - OMi gives no body dimensions for this part (M1@DRIVE, N5@DRIVE, N1@DRIVE, Y1@HEX, D@BORE, D1@BORE); the Brennan catalog TFA p52 (MJ-MP-FP TEE) prints them, but a Brennan-only value is not filled until Q-BRENNAN-ONLY is answered (proposals/); also no female-port tap drill / thread length source | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1057,6 +1083,11 @@
       <c r="T10" t="inlineStr">
         <is>
           <t>2611-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
